--- a/Lyme_by_County_2000_2025.xlsx
+++ b/Lyme_by_County_2000_2025.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{4D8F8D8C-FC42-424D-BC04-DBE8A4A21286}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1480" windowWidth="28220" windowHeight="20120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="100" yWindow="600" windowWidth="28220" windowHeight="17400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
